--- a/adhesome_atlas/files/fibronectin_like_candidate.xlsx
+++ b/adhesome_atlas/files/fibronectin_like_candidate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eaasa\Desktop\Evans_PHD_Thesis\Integrin_analysis\adhesome_atlas\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E59E09-E6C2-491B-ACA6-321E3603EB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7137EAF-218C-46AA-9E45-A6E23E0E7322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19290" yWindow="-8980" windowWidth="19380" windowHeight="20970" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27030" yWindow="-1560" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Family_assignment_rule" sheetId="12" r:id="rId1"/>
@@ -23,7 +23,8 @@
     <sheet name="Sources" sheetId="13" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Candidates!$A$1:$BD$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Candidates!$A$1:$BC$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">motif_scan_hits!$A$1:$AD$1</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -3372,7 +3373,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3417,6 +3418,13 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -3589,7 +3597,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3708,6 +3716,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5589,7 +5603,7 @@
       <c r="BA9" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="BB9" s="33" t="s">
+      <c r="BB9" s="41" t="s">
         <v>440</v>
       </c>
       <c r="BC9" s="3" t="s">
@@ -5803,7 +5817,7 @@
       <c r="M11" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="N11" s="3" t="s">
+      <c r="N11" s="42" t="s">
         <v>362</v>
       </c>
       <c r="O11" s="4">
@@ -7332,7 +7346,7 @@
       <c r="BA20" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="BB20" s="33" t="s">
+      <c r="BB20" s="41" t="s">
         <v>339</v>
       </c>
       <c r="BC20" s="3" t="s">
@@ -8466,7 +8480,7 @@
       <c r="M28" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="N28" s="3" t="s">
+      <c r="N28" s="42" t="s">
         <v>605</v>
       </c>
       <c r="O28" s="4">
@@ -12591,7 +12605,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="55" spans="1:55" s="2" customFormat="1" ht="87" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:55" s="2" customFormat="1" ht="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
         <v>219</v>
       </c>
@@ -13832,7 +13846,7 @@
       <c r="BA62" s="34" t="s">
         <v>367</v>
       </c>
-      <c r="BB62" s="33" t="s">
+      <c r="BB62" s="41" t="s">
         <v>764</v>
       </c>
       <c r="BC62" s="3" t="s">
@@ -17968,7 +17982,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BD88" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <conditionalFormatting sqref="AB2:AB88">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>AB2="Schistosoma-only in sampled HOG"</formula>
@@ -22913,6 +22926,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AD1" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
